--- a/output/pdf_financials_xlsx/MAL.xlsx
+++ b/output/pdf_financials_xlsx/MAL.xlsx
@@ -2391,25 +2391,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>22.641</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>22.641</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>26.52</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>26.502</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.645</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.538</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>7.606</v>
@@ -2424,19 +2424,19 @@
         <v>69.637</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>32.482</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>40.94</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>8.709</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>56.437</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>64.047</v>
       </c>
     </row>
     <row r="35">
@@ -2511,25 +2511,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>22.641</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>22.641</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>26.52</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>26.502</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.645</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5.538</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>7.606</v>
@@ -2544,19 +2544,19 @@
         <v>69.637</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>32.482</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>40.94</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>8.709</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>56.437</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>64.047</v>
       </c>
     </row>
     <row r="37">
@@ -3231,25 +3231,25 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>450.52</v>
+        <v>427.879</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>61.099</v>
+        <v>38.458</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>31.846</v>
+        <v>5.326</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.091</v>
+        <v>4.589</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.221</v>
+        <v>12.461</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>15.041</v>
+        <v>12.396</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>36.354</v>
+        <v>30.816</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>25.132</v>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -31199,7 +31199,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -63387,7 +63387,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -64727,7 +64727,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">

--- a/output/pdf_financials_xlsx/MAL.xlsx
+++ b/output/pdf_financials_xlsx/MAL.xlsx
@@ -7143,49 +7143,49 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>32.742</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.411</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="113">
@@ -37011,7 +37011,11 @@
           <t>Proceeds from disposal of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -43313,7 +43317,11 @@
           <t>Proceeds from disposal of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -50004,7 +50012,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -56330,7 +56342,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -58338,7 +58354,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MAL.xlsx
+++ b/output/pdf_financials_xlsx/MAL.xlsx
@@ -2757,37 +2757,37 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>27.964</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>38.975</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>37.278</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>36.699</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>44.004</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>32.698</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>16.009</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>21.018</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>29.719</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>23.98</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>33.961</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0</v>
@@ -2817,37 +2817,37 @@
         <v>97.553</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>106.48</v>
+        <v>134.444</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>106.392</v>
+        <v>145.367</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>146.969</v>
+        <v>184.247</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>160.989</v>
+        <v>197.688</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>207.189</v>
+        <v>251.193</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>205.609</v>
+        <v>238.307</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>196.756</v>
+        <v>212.765</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>187.897</v>
+        <v>208.915</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>177.801</v>
+        <v>207.52</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>164.234</v>
+        <v>188.214</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>169.562</v>
+        <v>203.523</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>211.364</v>
@@ -3237,31 +3237,31 @@
         <v>38.458</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.326</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.589</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12.461</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>12.396</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>30.816</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>25.132</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>69.55800000000001</v>
+        <v>53.549</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>86.494</v>
+        <v>65.476</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>99.09399999999999</v>
+        <v>69.375</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -4249,46 +4249,46 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>52.685</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>58.271</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>61.327</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>64.16</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>73.14700000000001</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>90.369</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>84.67700000000001</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>86.754</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>85.581</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>52.101</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>69.316</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>65.97799999999999</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>58.984</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>69.384</v>
       </c>
     </row>
     <row r="65">
@@ -4429,46 +4429,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>47.567</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>60.331</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>74.291</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>71.029</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>82.908</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>85.30500000000001</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>60.202</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>55.981</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>53.159</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>49.949</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>62.287</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>72.855</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>75.339</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>70.95699999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4489,46 +4489,46 @@
         <v>0</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>100.252</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>118.602</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>135.618</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>135.189</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>156.055</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>175.674</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>144.879</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>142.735</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>138.74</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>102.05</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>131.603</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>138.833</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>134.323</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0</v>
+        <v>140.341</v>
       </c>
     </row>
     <row r="69">
@@ -4909,31 +4909,31 @@
         <v>245.002</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>118.535</v>
+        <v>18.283</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>117.848</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>284.487</v>
+        <v>148.869</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>176.992</v>
+        <v>41.803</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>213.441</v>
+        <v>57.386</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>229.353</v>
+        <v>53.679</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>223.113</v>
+        <v>78.23399999999999</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>198.8</v>
+        <v>56.065</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>200.051</v>
+        <v>61.311</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0</v>
@@ -7023,31 +7023,31 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>1.093</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>3.155</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>-0.916</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.876</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -7724,16 +7724,16 @@
         <v>0</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-2.062</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-1.622</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-0.9370000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7808,25 +7808,25 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>12.813</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>21.011</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>6.334</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>-35.745</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>-4.972</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="J123" s="3" t="n">
         <v>0</v>
@@ -7835,16 +7835,16 @@
         <v>0</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>-15.165</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0</v>
+        <v>-4.124</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>0</v>
+        <v>-1.516</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
+        <v>-2.047</v>
       </c>
       <c r="P123" s="3" t="n">
         <v>0</v>
@@ -7928,25 +7928,25 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>12.813</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>21.011</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>6.334</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-35.745</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-4.972</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -7955,16 +7955,16 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-15.165</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-4.124</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-1.516</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-2.047</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -8206,10 +8206,10 @@
         <v>-38.505</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0</v>
+        <v>-1.511</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>0</v>
+        <v>13.111</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>-41.229</v>
@@ -8273,75 +8273,47 @@
       <c r="D130" s="3" t="n">
         <v>22.641</v>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>24.952</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>26.502</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>22.423</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>5.538</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>7.606</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>40.394</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>63.316</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>113.938</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>32.482</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="Q130" s="3" t="n">
+        <v>8.709</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>56.437</v>
       </c>
     </row>
     <row r="131">
@@ -8422,46 +8394,46 @@
         <v>2.311</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>3.079</v>
+        <v>1.568</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>-17.19</v>
+        <v>-4.079</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>-15.799</v>
+        <v>-14.663</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>-5.512</v>
+        <v>-5.115</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>0.955</v>
+        <v>2.893</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>155.001</v>
+        <v>2.068</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>129.949</v>
+        <v>32.788</v>
       </c>
       <c r="L132" s="3" t="n">
-        <v>99.997</v>
+        <v>22.922</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>104.205</v>
+        <v>6.321</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>-81.28700000000001</v>
+        <v>-81.456</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>8.41</v>
+        <v>8.458</v>
       </c>
       <c r="P132" s="3" t="n">
-        <v>-32.774</v>
+        <v>-32.231</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>46.57</v>
+        <v>47.728</v>
       </c>
       <c r="R132" s="3" t="n">
-        <v>8.063000000000001</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="133">
@@ -8481,75 +8453,47 @@
       <c r="D133" s="3" t="n">
         <v>24.952</v>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>22.423</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>5.538</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>7.606</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>40.394</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>63.316</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>69.637</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>32.482</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>8.709</v>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>56.437</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>64.047</v>
       </c>
     </row>
     <row r="134">
@@ -37789,7 +37733,11 @@
           <t>Share repurchases 21</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -38177,7 +38125,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -38353,7 +38305,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -40810,7 +40766,11 @@
           <t>Cash at end of the year X</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -41004,7 +40964,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -43715,7 +43679,11 @@
           <t>Decrease in long–term debt 14, 18</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -44109,7 +44077,11 @@
           <t>Share repurchases 20</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -45620,7 +45592,11 @@
           <t>Decrease in long-term debt 14,18</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -46016,7 +45992,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -46214,7 +46194,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -46812,7 +46796,11 @@
           <t>Accretion 26</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -47909,7 +47897,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -48107,7 +48099,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -48505,7 +48501,11 @@
           <t>Accretion 25</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -49109,7 +49109,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -49208,7 +49212,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -49606,7 +49614,11 @@
           <t>Accretion 23</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -50212,7 +50224,11 @@
           <t>Increase in long-term debt 12</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -50509,7 +50525,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -50608,7 +50628,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -51004,7 +51028,11 @@
           <t>Accretion 23</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -51994,7 +52022,11 @@
           <t>Decrease in long-term debt 12</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -52883,7 +52915,11 @@
           <t>Accretion 22</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -53786,7 +53822,11 @@
           <t>Decrease in long-term debt 11</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -54952,7 +54992,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -56140,7 +56184,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -56445,7 +56493,11 @@
           <t>Increase in long-term debt 11</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -56942,7 +56994,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -57041,7 +57097,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -57847,7 +57907,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -58857,7 +58921,11 @@
           <t>Decrease in long-term debt 10</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -58956,7 +59024,11 @@
           <t>Increase in long-term debt 10</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -59651,7 +59723,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -59849,7 +59925,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -61556,7 +61636,11 @@
           <t>Decrease in long-term debt</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -61655,7 +61739,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
